--- a/基本設計/07_タスク管理_画面基本設計書.xlsx
+++ b/基本設計/07_タスク管理_画面基本設計書.xlsx
@@ -2,18 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R1c4442170b884d5e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R600eac8d11a040aa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_画面一覧" sheetId="13" r:id="R14d7be8eb2154f46"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_画面遷移" sheetId="14" r:id="R858f803ab6df478d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_画面項目定義" sheetId="16" r:id="R7ee762a007104e2f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_画面処理概要" sheetId="18" r:id="R873cc36d190b4aae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WF_SCR-013_タスク一覧" sheetId="19" r:id="R478cd850c537454a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WF_SCR-014_マイタスク" sheetId="20" r:id="Rf0814493f4ce4340"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WF_SCR-015_タスク登録" sheetId="21" r:id="R8aa9991a35044d75"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WF_SCR-016_タスク編集" sheetId="22" r:id="Rfb6529db4a5344c7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WF_SCR-017_タスク詳細" sheetId="23" r:id="R4378dfb7f6174ec8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WF_SCR-018_タスクボード" sheetId="24" r:id="R5ffbf53b923e4270"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="Rfa61316561984ec9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="Ra94cd38dfd8b4ef4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_画面一覧" sheetId="13" r:id="R19e95c3e1da04a22"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_画面遷移" sheetId="14" r:id="R3cbcabadd1134e7d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_画面項目定義" sheetId="16" r:id="Rf4e0363ab80148e5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_画面処理概要" sheetId="18" r:id="R624252b6fde1413e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WF_SCR-013_タスク一覧" sheetId="19" r:id="R0042a40aaa474edc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WF_SCR-014_マイタスク" sheetId="20" r:id="R3649c3ac37ba4860"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WF_SCR-015_タスク登録" sheetId="21" r:id="R704c19592b7e423c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WF_SCR-016_タスク編集" sheetId="22" r:id="Rd25886c49c6e408f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WF_SCR-017_タスク詳細" sheetId="23" r:id="R8256f2dff2664797"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WF_SCR-018_タスクボード" sheetId="24" r:id="Rb90cf6e4e1f74039"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1800,10 +1800,7 @@
       <x:c r="F16" s="339"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" t="str">
-        <x:v>本書は Company WorkHub の基本設計内容を定義する。
-Ver.1.8 は状態変更入口、API/DB制約、取込Transaction、日報一意制約、通知・Token保持を整合した再Review対応版である。</x:v>
-      </x:c>
+      <x:c r="A17"/>
       <x:c r="C17"/>
       <x:c r="D17"/>
       <x:c r="E17"/>
@@ -1819,25 +1816,22 @@
     </x:row>
     <x:row r="19">
       <x:c r="A19"/>
-      <x:c r="B19" s="382" t="str">
-        <x:v>本書は Company WorkHub の基本設計内容を定義する。
-Ver.1.7 は状態変更入口、API/DB制約、取込Transaction、日報一意制約、通知・Token保持を整合した再Review対応版である。</x:v>
-      </x:c>
-      <x:c r="C19" s="382"/>
-      <x:c r="D19" s="382"/>
-      <x:c r="E19" s="382"/>
-      <x:c r="F19" s="382"/>
-      <x:c r="G19" s="382"/>
-      <x:c r="H19" s="382"/>
+      <x:c r="B19"/>
+      <x:c r="C19"/>
+      <x:c r="D19"/>
+      <x:c r="E19"/>
+      <x:c r="F19"/>
+      <x:c r="G19"/>
+      <x:c r="H19"/>
     </x:row>
     <x:row r="20">
-      <x:c r="B20" s="382"/>
-      <x:c r="C20" s="382"/>
-      <x:c r="D20" s="382"/>
-      <x:c r="E20" s="382"/>
-      <x:c r="F20" s="382"/>
-      <x:c r="G20" s="382"/>
-      <x:c r="H20" s="382"/>
+      <x:c r="B20"/>
+      <x:c r="C20"/>
+      <x:c r="D20"/>
+      <x:c r="E20"/>
+      <x:c r="F20"/>
+      <x:c r="G20"/>
+      <x:c r="H20"/>
     </x:row>
     <x:row r="21">
       <x:c r="B21" s="382"/>
@@ -3391,54 +3385,22 @@
       <x:c r="P31" s="48"/>
     </x:row>
     <x:row r="32" ht="21" customHeight="1">
-      <x:c r="A32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="B32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="C32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="D32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="E32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="F32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="G32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="H32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="I32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="J32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="K32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="L32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="M32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="N32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="O32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="P32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
+      <x:c r="A32"/>
+      <x:c r="B32"/>
+      <x:c r="C32"/>
+      <x:c r="D32"/>
+      <x:c r="E32"/>
+      <x:c r="F32"/>
+      <x:c r="G32"/>
+      <x:c r="H32"/>
+      <x:c r="I32"/>
+      <x:c r="J32"/>
+      <x:c r="K32"/>
+      <x:c r="L32"/>
+      <x:c r="M32"/>
+      <x:c r="N32"/>
+      <x:c r="O32"/>
+      <x:c r="P32"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -5098,54 +5060,22 @@
       <x:c r="P31" s="48"/>
     </x:row>
     <x:row r="32" ht="21" customHeight="1">
-      <x:c r="A32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="B32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="C32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="D32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="E32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="F32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="G32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="H32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="I32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="J32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="K32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="L32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="M32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="N32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="O32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="P32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
+      <x:c r="A32"/>
+      <x:c r="B32"/>
+      <x:c r="C32"/>
+      <x:c r="D32"/>
+      <x:c r="E32"/>
+      <x:c r="F32"/>
+      <x:c r="G32"/>
+      <x:c r="H32"/>
+      <x:c r="I32"/>
+      <x:c r="J32"/>
+      <x:c r="K32"/>
+      <x:c r="L32"/>
+      <x:c r="M32"/>
+      <x:c r="N32"/>
+      <x:c r="O32"/>
+      <x:c r="P32"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -7703,54 +7633,22 @@
       <x:c r="P31" s="48"/>
     </x:row>
     <x:row r="32" ht="21" customHeight="1">
-      <x:c r="A32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="B32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="C32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="D32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="E32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="F32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="G32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="H32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="I32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="J32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="K32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="L32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="M32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="N32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="O32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="P32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
+      <x:c r="A32"/>
+      <x:c r="B32"/>
+      <x:c r="C32"/>
+      <x:c r="D32"/>
+      <x:c r="E32"/>
+      <x:c r="F32"/>
+      <x:c r="G32"/>
+      <x:c r="H32"/>
+      <x:c r="I32"/>
+      <x:c r="J32"/>
+      <x:c r="K32"/>
+      <x:c r="L32"/>
+      <x:c r="M32"/>
+      <x:c r="N32"/>
+      <x:c r="O32"/>
+      <x:c r="P32"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -13783,54 +13681,22 @@
       <x:c r="P31" s="48"/>
     </x:row>
     <x:row r="32" ht="21" customHeight="1">
-      <x:c r="A32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="B32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="C32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="D32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="E32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="F32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="G32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="H32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="I32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="J32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="K32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="L32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="M32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="N32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="O32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="P32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
+      <x:c r="A32"/>
+      <x:c r="B32"/>
+      <x:c r="C32"/>
+      <x:c r="D32"/>
+      <x:c r="E32"/>
+      <x:c r="F32"/>
+      <x:c r="G32"/>
+      <x:c r="H32"/>
+      <x:c r="I32"/>
+      <x:c r="J32"/>
+      <x:c r="K32"/>
+      <x:c r="L32"/>
+      <x:c r="M32"/>
+      <x:c r="N32"/>
+      <x:c r="O32"/>
+      <x:c r="P32"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -15455,54 +15321,22 @@
       <x:c r="P31" s="48"/>
     </x:row>
     <x:row r="32" ht="21" customHeight="1">
-      <x:c r="A32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="B32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="C32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="D32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="E32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="F32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="G32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="H32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="I32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="J32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="K32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="L32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="M32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="N32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="O32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="P32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
+      <x:c r="A32"/>
+      <x:c r="B32"/>
+      <x:c r="C32"/>
+      <x:c r="D32"/>
+      <x:c r="E32"/>
+      <x:c r="F32"/>
+      <x:c r="G32"/>
+      <x:c r="H32"/>
+      <x:c r="I32"/>
+      <x:c r="J32"/>
+      <x:c r="K32"/>
+      <x:c r="L32"/>
+      <x:c r="M32"/>
+      <x:c r="N32"/>
+      <x:c r="O32"/>
+      <x:c r="P32"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -17084,54 +16918,22 @@
       <x:c r="P31" s="48"/>
     </x:row>
     <x:row r="32" ht="21" customHeight="1">
-      <x:c r="A32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="B32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="C32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="D32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="E32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="F32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="G32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="H32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="I32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="J32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="K32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="L32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="M32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="N32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="O32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="P32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
+      <x:c r="A32"/>
+      <x:c r="B32"/>
+      <x:c r="C32"/>
+      <x:c r="D32"/>
+      <x:c r="E32"/>
+      <x:c r="F32"/>
+      <x:c r="G32"/>
+      <x:c r="H32"/>
+      <x:c r="I32"/>
+      <x:c r="J32"/>
+      <x:c r="K32"/>
+      <x:c r="L32"/>
+      <x:c r="M32"/>
+      <x:c r="N32"/>
+      <x:c r="O32"/>
+      <x:c r="P32"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
